--- a/artfynd/A 69777-2021 artfynd.xlsx
+++ b/artfynd/A 69777-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69777-2021 artfynd.xlsx
+++ b/artfynd/A 69777-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17264815</v>
+        <v>17264813</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565584.5462026219</v>
+        <v>565596</v>
       </c>
       <c r="R2" t="n">
-        <v>6615930.308227831</v>
+        <v>6615942</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,19 +753,9 @@
           <t>2015-03-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-03-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,19 +793,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17264813</v>
+        <v>17264815</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -843,7 +823,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565596.4927210779</v>
+        <v>565585</v>
       </c>
       <c r="R3" t="n">
-        <v>6615941.631890718</v>
+        <v>6615930</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -891,19 +871,9 @@
           <t>2015-03-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,6 +908,344 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17264818</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brinken SO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565642</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6615939</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-03-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-03-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal granskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>I mosstäcke</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>56958262</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91893</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brinken SO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565642</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6615939</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>56958269</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brinken SO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565642</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6615939</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69777-2021 artfynd.xlsx
+++ b/artfynd/A 69777-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17264813</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17264815</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17264818</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56958262</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,8 +1271,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56958269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>